--- a/InputData/trans/EoVPwFE/Elasticity of Veh Price wrt Fuel Econ.xlsx
+++ b/InputData/trans/EoVPwFE/Elasticity of Veh Price wrt Fuel Econ.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28221"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Meghan\Dropbox (Energy Innovation)\EPS Versions\eps-1.5.0-us-wipL\InputData\trans\EoVPwFE\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_9B1F04DFBCB6E5E0BA2EE1E525DD8D6BFF071B41" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="75" windowWidth="23955" windowHeight="13095"/>
+    <workbookView xWindow="120" yWindow="75" windowWidth="23955" windowHeight="13095" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -17,15 +18,41 @@
     <sheet name="EoVPwFE" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="37">
   <si>
+    <t>EoVPwFE Elasticity of Vehicle Price wrt Fuel Economy</t>
+  </si>
+  <si>
     <t>Source:</t>
   </si>
   <si>
+    <t>Incremental Cost for Fuel Economy</t>
+  </si>
+  <si>
+    <t>U.S. Environmental Protection Agency</t>
+  </si>
+  <si>
+    <t>EPA and NHTSA Set Standards to Reduce Greenhouse Gases and Improve Fuel Economy for Model Years 2017-2025 Cars and Light Trucks</t>
+  </si>
+  <si>
+    <t>http://www.epa.gov/otaq/climate/documents/420f12051.pdf</t>
+  </si>
+  <si>
+    <t>Page 2</t>
+  </si>
+  <si>
+    <t>Passenger LDV Base Cost</t>
+  </si>
+  <si>
     <t>Center for Automotive Research</t>
   </si>
   <si>
@@ -38,27 +65,42 @@
     <t>Page 24, Figure 9</t>
   </si>
   <si>
-    <t>Incremental Cost for Fuel Economy</t>
-  </si>
-  <si>
-    <t>U.S. Environmental Protection Agency</t>
-  </si>
-  <si>
-    <t>EPA and NHTSA Set Standards to Reduce Greenhouse Gases and Improve Fuel Economy for Model Years 2017-2025 Cars and Light Trucks</t>
-  </si>
-  <si>
-    <t>http://www.epa.gov/otaq/climate/documents/420f12051.pdf</t>
-  </si>
-  <si>
-    <t>Page 2</t>
-  </si>
-  <si>
-    <t>Passenger LDV Base Cost</t>
+    <t>Currency Year</t>
+  </si>
+  <si>
+    <t>The model uses LDVs elasticity for all vehicle types because no data on price elasticity</t>
+  </si>
+  <si>
+    <t>of other vehicle types with respect to fuel economy is available.</t>
+  </si>
+  <si>
+    <t>The EPA and NHTSA document does not explicitly specify its curency year, and</t>
+  </si>
+  <si>
+    <t>it discusses costs in years 2017-2025, so we assume it is using currency of the year</t>
+  </si>
+  <si>
+    <t>of the document's publication, which is 2012.  Hence, no adjustment is needed.</t>
+  </si>
+  <si>
+    <t>The Center for Automotive Research's data was taken from a 2010 Automotive Yearbook</t>
+  </si>
+  <si>
+    <t>and therefore likely is in 2010 dollars.</t>
+  </si>
+  <si>
+    <t>We adjust 2010 dollars to 2012 dollars using the following conversion factor:</t>
+  </si>
+  <si>
+    <t>See "cpi.xlsx" in the InputData folder for source information.</t>
   </si>
   <si>
     <t>2016 Model Year MPG</t>
   </si>
   <si>
+    <t>From U.S. EPA</t>
+  </si>
+  <si>
     <t>2025 Model Year MPG</t>
   </si>
   <si>
@@ -68,18 +110,21 @@
     <t>Base LDV Cost</t>
   </si>
   <si>
+    <t>From Center for Automotive Research (2010$)</t>
+  </si>
+  <si>
     <t>2016 Model Year Cost</t>
   </si>
   <si>
+    <t>In 2012$ dollars</t>
+  </si>
+  <si>
     <t>2025 Model Year Cost</t>
   </si>
   <si>
     <t>Assumes EPA value of $1800 is in real dollars</t>
   </si>
   <si>
-    <t>From U.S. EPA</t>
-  </si>
-  <si>
     <t>% Improvement in Fuel Economy</t>
   </si>
   <si>
@@ -89,60 +134,21 @@
     <t>Elasticity</t>
   </si>
   <si>
-    <t>EoVPwFE Elasticity of Vehicle Price wrt Fuel Economy</t>
+    <t>Elasticity (dimensionless)</t>
   </si>
   <si>
     <t>Vehicle Price wrt Fuel Econ</t>
   </si>
-  <si>
-    <t>See "cpi.xlsx" in the InputData folder for source information.</t>
-  </si>
-  <si>
-    <t>The EPA and NHTSA document does not explicitly specify its curency year, and</t>
-  </si>
-  <si>
-    <t>it discusses costs in years 2017-2025, so we assume it is using currency of the year</t>
-  </si>
-  <si>
-    <t>of the document's publication, which is 2012.  Hence, no adjustment is needed.</t>
-  </si>
-  <si>
-    <t>The Center for Automotive Research's data was taken from a 2010 Automotive Yearbook</t>
-  </si>
-  <si>
-    <t>and therefore likely is in 2010 dollars.</t>
-  </si>
-  <si>
-    <t>We adjust 2010 dollars to 2012 dollars using the following conversion factor:</t>
-  </si>
-  <si>
-    <t>Currency Year</t>
-  </si>
-  <si>
-    <t>From Center for Automotive Research (2010$)</t>
-  </si>
-  <si>
-    <t>In 2012$ dollars</t>
-  </si>
-  <si>
-    <t>The model uses LDVs elasticity for all vehicle types because no data on price elasticity</t>
-  </si>
-  <si>
-    <t>of other vehicle types with respect to fuel economy is available.</t>
-  </si>
-  <si>
-    <t>Elasticity (dimensionless)</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -277,7 +283,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -291,23 +297,20 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="9">
-    <cellStyle name="Body: normal cell" xfId="6"/>
-    <cellStyle name="Font: Calibri, 9pt regular" xfId="4"/>
-    <cellStyle name="Footnotes: top row" xfId="8"/>
-    <cellStyle name="Header: bottom row" xfId="5"/>
+    <cellStyle name="Body: normal cell" xfId="6" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="Font: Calibri, 9pt regular" xfId="4" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Footnotes: top row" xfId="8" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Header: bottom row" xfId="5" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Parent row" xfId="7"/>
+    <cellStyle name="Parent row" xfId="7" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
-    <cellStyle name="Table title" xfId="3"/>
+    <cellStyle name="Table title" xfId="3" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -323,9 +326,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -363,9 +366,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -400,7 +403,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -435,7 +438,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -608,144 +611,144 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.28515625" customWidth="1"/>
     <col min="2" max="2" width="57.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="B4" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
       <c r="B5" s="3">
         <v>2012</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2">
       <c r="B6" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="B7" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="B8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="B10" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B7" s="4" t="s">
+    <row r="11" spans="1:2">
+      <c r="B11" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B10" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B11" s="3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2">
       <c r="B12" s="3">
         <v>2011</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2">
       <c r="B13" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
       <c r="B14" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
       <c r="B15" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="11" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="9" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="9" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="11"/>
-    </row>
-    <row r="21" spans="1:1" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="9" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="9" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="9" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="10" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="1"/>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27">
         <v>1.0549999999999999</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" s="10" t="s">
-        <v>24</v>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B14" r:id="rId1"/>
-    <hyperlink ref="B7" r:id="rId2"/>
+    <hyperlink ref="B14" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="B7" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId3"/>
@@ -753,64 +756,64 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.42578125" customWidth="1"/>
     <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B1">
         <v>35.5</v>
       </c>
       <c r="D1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B2">
         <v>54.5</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B3" s="5">
         <v>1800</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="B4" s="5">
         <v>23186</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="B5" s="5">
         <f>B4*About!A27</f>
@@ -818,12 +821,12 @@
       </c>
       <c r="C5" s="5"/>
       <c r="D5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="B6" s="5">
         <f>B5+B3</f>
@@ -831,30 +834,30 @@
       </c>
       <c r="C6" s="5"/>
       <c r="D6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="B8" s="6">
         <f>(B2-B1)/B1</f>
         <v>0.53521126760563376</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="B9" s="6">
         <f>(B6-B5)/B5</f>
         <v>7.358583358236688E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="B11" s="7">
         <f>B9/B8</f>
@@ -867,24 +870,24 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="27.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="B1" s="12" t="s">
+    <row r="1" spans="1:2" ht="45">
+      <c r="B1" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="14.45">
+      <c r="A2" t="s">
         <v>36</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="14.45" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>23</v>
       </c>
       <c r="B2" s="8">
         <f>Calculations!B11</f>
@@ -894,4 +897,175 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A251C7805F896F47A4F48569C73A0799" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7abd873f26c83d98889b6bc5171c7cdd">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="295384f30983e71c631053ca9b14fb23" ns2:_="">
+    <xsd:import namespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2B7FF9F0-F3A3-4AFE-88C0-06C6A08E672C}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5EA6AB2C-85FB-4E9B-8735-684CBA17D18F}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65361301-8979-497A-9FAB-2473040CAB0C}"/>
 </file>